--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N82_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N82_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>29.2922164087658</v>
+        <v>4.759985166424443</v>
       </c>
       <c r="D2" t="n">
-        <v>28.65990236644919</v>
+        <v>4.657234134547994</v>
       </c>
       <c r="E2" t="n">
-        <v>11.62683436579484</v>
+        <v>1.889360584441662</v>
       </c>
       <c r="F2" t="n">
-        <v>9.992654872103245</v>
+        <v>1.623806416716777</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.54100848775103</v>
+        <v>3.175413879259543</v>
       </c>
       <c r="D3" t="n">
-        <v>16.59059470232569</v>
+        <v>2.695971639127925</v>
       </c>
       <c r="E3" t="n">
-        <v>11.62683436579484</v>
+        <v>1.889360584441662</v>
       </c>
       <c r="F3" t="n">
-        <v>9.992654872103245</v>
+        <v>1.623806416716777</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>1.219970432717676</v>
+        <v>0.1982451953166224</v>
       </c>
       <c r="D4" t="n">
-        <v>4.163122585018896</v>
+        <v>0.6765074200655706</v>
       </c>
       <c r="E4" t="n">
-        <v>11.62683436579484</v>
+        <v>1.889360584441662</v>
       </c>
       <c r="F4" t="n">
-        <v>9.992654872103245</v>
+        <v>1.623806416716777</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>5.635143732902869</v>
+        <v>0.9157108565967162</v>
       </c>
       <c r="D5" t="n">
-        <v>8.857891502938191</v>
+        <v>1.439407369227456</v>
       </c>
       <c r="E5" t="n">
-        <v>11.62683436579484</v>
+        <v>1.889360584441662</v>
       </c>
       <c r="F5" t="n">
-        <v>9.992654872103245</v>
+        <v>1.623806416716777</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>1.835727038021387</v>
+        <v>0.2983056436784755</v>
       </c>
       <c r="D6" t="n">
-        <v>9.694964030726599</v>
+        <v>1.575431654993072</v>
       </c>
       <c r="E6" t="n">
-        <v>11.62683436579484</v>
+        <v>1.889360584441662</v>
       </c>
       <c r="F6" t="n">
-        <v>9.992654872103245</v>
+        <v>1.623806416716777</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>9.422022782507311</v>
+        <v>1.531078702157438</v>
       </c>
       <c r="D7" t="n">
-        <v>9.938185278267406</v>
+        <v>1.614955107718454</v>
       </c>
       <c r="E7" t="n">
-        <v>11.62683436579484</v>
+        <v>1.889360584441662</v>
       </c>
       <c r="F7" t="n">
-        <v>9.992654872103245</v>
+        <v>1.623806416716777</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>20.31123552889676</v>
+        <v>3.300575773445724</v>
       </c>
       <c r="D8" t="n">
-        <v>20.05557193011914</v>
+        <v>3.25903043864436</v>
       </c>
       <c r="E8" t="n">
-        <v>11.62683436579484</v>
+        <v>1.889360584441662</v>
       </c>
       <c r="F8" t="n">
-        <v>9.992654872103245</v>
+        <v>1.623806416716777</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>24.98745093840978</v>
+        <v>4.060460777491589</v>
       </c>
       <c r="D9" t="n">
-        <v>21.71627953965334</v>
+        <v>3.528895425193667</v>
       </c>
       <c r="E9" t="n">
-        <v>11.62683436579484</v>
+        <v>1.889360584441662</v>
       </c>
       <c r="F9" t="n">
-        <v>9.992654872103245</v>
+        <v>1.623806416716777</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>21.90748765178123</v>
+        <v>3.55996674341445</v>
       </c>
       <c r="D10" t="n">
-        <v>21.15906113181083</v>
+        <v>3.438347433919259</v>
       </c>
       <c r="E10" t="n">
-        <v>11.62683436579484</v>
+        <v>1.889360584441662</v>
       </c>
       <c r="F10" t="n">
-        <v>9.992654872103245</v>
+        <v>1.623806416716777</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>23.0692623094882</v>
+        <v>3.748755125291832</v>
       </c>
       <c r="D11" t="n">
-        <v>20.3138828090274</v>
+        <v>3.301005956466952</v>
       </c>
       <c r="E11" t="n">
-        <v>11.62683436579484</v>
+        <v>1.889360584441662</v>
       </c>
       <c r="F11" t="n">
-        <v>9.992654872103245</v>
+        <v>1.623806416716777</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>34.33559267498997</v>
+        <v>5.57953380968587</v>
       </c>
       <c r="D12" t="n">
-        <v>30.2618394486491</v>
+        <v>4.917548910405479</v>
       </c>
       <c r="E12" t="n">
-        <v>11.62683436579484</v>
+        <v>1.889360584441662</v>
       </c>
       <c r="F12" t="n">
-        <v>9.992654872103245</v>
+        <v>1.623806416716777</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>30.99024293585684</v>
+        <v>5.035914477076737</v>
       </c>
       <c r="D13" t="n">
-        <v>19.63588518423476</v>
+        <v>3.190831342438148</v>
       </c>
       <c r="E13" t="n">
-        <v>11.62683436579484</v>
+        <v>1.889360584441662</v>
       </c>
       <c r="F13" t="n">
-        <v>9.992654872103245</v>
+        <v>1.623806416716777</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>30.59665555782398</v>
+        <v>4.971956528146396</v>
       </c>
       <c r="D14" t="n">
-        <v>6.032741058744228</v>
+        <v>0.9803204220459371</v>
       </c>
       <c r="E14" t="n">
-        <v>11.62683436579484</v>
+        <v>1.889360584441662</v>
       </c>
       <c r="F14" t="n">
-        <v>9.992654872103245</v>
+        <v>1.623806416716777</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>31.0152512774844</v>
+        <v>5.039978332591216</v>
       </c>
       <c r="D15" t="n">
-        <v>1.001968458586928</v>
+        <v>0.1628198745203758</v>
       </c>
       <c r="E15" t="n">
-        <v>11.62683436579484</v>
+        <v>1.889360584441662</v>
       </c>
       <c r="F15" t="n">
-        <v>9.992654872103245</v>
+        <v>1.623806416716777</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>39.00662990410684</v>
+        <v>6.338577359417362</v>
       </c>
       <c r="D16" t="n">
-        <v>11.14605039911452</v>
+        <v>1.811233189856109</v>
       </c>
       <c r="E16" t="n">
-        <v>11.62683436579484</v>
+        <v>1.889360584441662</v>
       </c>
       <c r="F16" t="n">
-        <v>9.992654872103245</v>
+        <v>1.623806416716777</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>36.24754578558591</v>
+        <v>5.890226190157711</v>
       </c>
       <c r="D17" t="n">
-        <v>36.00422722331738</v>
+        <v>5.850686923789074</v>
       </c>
       <c r="E17" t="n">
-        <v>11.62683436579484</v>
+        <v>1.889360584441662</v>
       </c>
       <c r="F17" t="n">
-        <v>9.992654872103245</v>
+        <v>1.623806416716777</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>29.31147181862375</v>
+        <v>4.76311417052636</v>
       </c>
       <c r="D18" t="n">
-        <v>8.772912340249686</v>
+        <v>1.425598255290574</v>
       </c>
       <c r="E18" t="n">
-        <v>11.62683436579484</v>
+        <v>1.889360584441662</v>
       </c>
       <c r="F18" t="n">
-        <v>9.992654872103245</v>
+        <v>1.623806416716777</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31.3808195669552</v>
+        <v>5.09938317963022</v>
       </c>
       <c r="D19" t="n">
-        <v>31.16155754837238</v>
+        <v>5.063753101610512</v>
       </c>
       <c r="E19" t="n">
-        <v>11.62683436579484</v>
+        <v>1.889360584441662</v>
       </c>
       <c r="F19" t="n">
-        <v>9.992654872103245</v>
+        <v>1.623806416716777</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>23.78242443252391</v>
+        <v>3.864643970285135</v>
       </c>
       <c r="D20" t="n">
-        <v>23.53063265060839</v>
+        <v>3.823727805723863</v>
       </c>
       <c r="E20" t="n">
-        <v>11.62683436579484</v>
+        <v>1.889360584441662</v>
       </c>
       <c r="F20" t="n">
-        <v>9.992654872103245</v>
+        <v>1.623806416716777</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>49.42397929582864</v>
+        <v>8.031396635572154</v>
       </c>
       <c r="D21" t="n">
-        <v>36.48786487676068</v>
+        <v>5.929278042473611</v>
       </c>
       <c r="E21" t="n">
-        <v>11.62683436579484</v>
+        <v>1.889360584441662</v>
       </c>
       <c r="F21" t="n">
-        <v>9.992654872103245</v>
+        <v>1.623806416716777</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>30.0630240946688</v>
+        <v>4.88524141538368</v>
       </c>
       <c r="D22" t="n">
-        <v>29.86213272157639</v>
+        <v>4.852596567256164</v>
       </c>
       <c r="E22" t="n">
-        <v>11.62683436579484</v>
+        <v>1.889360584441662</v>
       </c>
       <c r="F22" t="n">
-        <v>9.992654872103245</v>
+        <v>1.623806416716777</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>27.15012371038308</v>
+        <v>4.41189510293725</v>
       </c>
       <c r="D23" t="n">
-        <v>27.44312177019566</v>
+        <v>4.459507287656796</v>
       </c>
       <c r="E23" t="n">
-        <v>11.62683436579484</v>
+        <v>1.889360584441662</v>
       </c>
       <c r="F23" t="n">
-        <v>9.992654872103245</v>
+        <v>1.623806416716777</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>19.5082955500468</v>
+        <v>3.170098026882604</v>
       </c>
       <c r="D24" t="n">
-        <v>19.3998294721919</v>
+        <v>3.152472289231184</v>
       </c>
       <c r="E24" t="n">
-        <v>11.62683436579484</v>
+        <v>1.889360584441662</v>
       </c>
       <c r="F24" t="n">
-        <v>9.992654872103245</v>
+        <v>1.623806416716777</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>6.461853492622825</v>
+        <v>1.050051192551209</v>
       </c>
       <c r="D25" t="n">
-        <v>6.566913452450231</v>
+        <v>1.067123436023163</v>
       </c>
       <c r="E25" t="n">
-        <v>11.62683436579484</v>
+        <v>1.889360584441662</v>
       </c>
       <c r="F25" t="n">
-        <v>9.992654872103245</v>
+        <v>1.623806416716777</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>18.94555705627861</v>
+        <v>3.078653021645274</v>
       </c>
       <c r="D26" t="n">
-        <v>18.64541559479454</v>
+        <v>3.029880034154113</v>
       </c>
       <c r="E26" t="n">
-        <v>11.62683436579484</v>
+        <v>1.889360584441662</v>
       </c>
       <c r="F26" t="n">
-        <v>9.992654872103245</v>
+        <v>1.623806416716777</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
